--- a/NIFTY_50_Technical_Metrics.xlsx
+++ b/NIFTY_50_Technical_Metrics.xlsx
@@ -1413,7 +1413,7 @@
         <v>44</v>
       </c>
       <c r="P2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q2">
         <v>2737.46</v>
@@ -1532,7 +1532,7 @@
         <v>97</v>
       </c>
       <c r="P3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q3">
         <v>1755.3</v>
@@ -1651,7 +1651,7 @@
         <v>66</v>
       </c>
       <c r="P4">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Q4">
         <v>7902</v>
@@ -1770,7 +1770,7 @@
         <v>50</v>
       </c>
       <c r="P5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q5">
         <v>2362.6</v>
@@ -1889,7 +1889,7 @@
         <v>77</v>
       </c>
       <c r="P6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q6">
         <v>1243.36</v>
@@ -2127,7 +2127,7 @@
         <v>28</v>
       </c>
       <c r="P8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q8">
         <v>1737.96</v>
@@ -2246,7 +2246,7 @@
         <v>52</v>
       </c>
       <c r="P9">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q9">
         <v>962.58</v>
@@ -2365,7 +2365,7 @@
         <v>30</v>
       </c>
       <c r="P10">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q10">
         <v>377.2</v>
@@ -2603,7 +2603,7 @@
         <v>34</v>
       </c>
       <c r="P12">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q12">
         <v>1322.14</v>
@@ -2722,7 +2722,7 @@
         <v>87</v>
       </c>
       <c r="P13">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q13">
         <v>414.43</v>
@@ -2841,7 +2841,7 @@
         <v>72</v>
       </c>
       <c r="P14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q14">
         <v>1198.36</v>
@@ -2960,7 +2960,7 @@
         <v>70</v>
       </c>
       <c r="P15">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q15">
         <v>6970</v>
@@ -3079,7 +3079,7 @@
         <v>89</v>
       </c>
       <c r="P16">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q16">
         <v>324.06</v>
@@ -3198,7 +3198,7 @@
         <v>56</v>
       </c>
       <c r="P17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q17">
         <v>2921.78</v>
@@ -3317,7 +3317,7 @@
         <v>64</v>
       </c>
       <c r="P18">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q18">
         <v>1196.98</v>
@@ -3436,7 +3436,7 @@
         <v>13</v>
       </c>
       <c r="P19">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q19">
         <v>703.7</v>
@@ -3555,7 +3555,7 @@
         <v>32</v>
       </c>
       <c r="P20">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q20">
         <v>544.4299999999999</v>
@@ -3674,7 +3674,7 @@
         <v>85</v>
       </c>
       <c r="P21">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q21">
         <v>916.05</v>
@@ -4031,7 +4031,7 @@
         <v>38</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q24">
         <v>4924.32</v>
@@ -4150,7 +4150,7 @@
         <v>23</v>
       </c>
       <c r="P25">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q25">
         <v>1009.35</v>
@@ -4269,7 +4269,7 @@
         <v>21</v>
       </c>
       <c r="P26">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q26">
         <v>264.46</v>
@@ -4388,7 +4388,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q27">
         <v>214.39</v>
@@ -4507,7 +4507,7 @@
         <v>60</v>
       </c>
       <c r="P28">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q28">
         <v>1213.62</v>
@@ -4626,7 +4626,7 @@
         <v>95</v>
       </c>
       <c r="P29">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q29">
         <v>432.78</v>
@@ -4745,7 +4745,7 @@
         <v>62</v>
       </c>
       <c r="P30">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q30">
         <v>3709.98</v>
@@ -4983,7 +4983,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q32">
         <v>11451</v>
@@ -5102,7 +5102,7 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q33">
         <v>896.9400000000001</v>
@@ -5340,7 +5340,7 @@
         <v>46</v>
       </c>
       <c r="P35">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q35">
         <v>316.34</v>
@@ -5459,7 +5459,7 @@
         <v>48</v>
       </c>
       <c r="P36">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q36">
         <v>222.41</v>
@@ -5578,7 +5578,7 @@
         <v>36</v>
       </c>
       <c r="P37">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q37">
         <v>252.21</v>
@@ -5697,7 +5697,7 @@
         <v>26</v>
       </c>
       <c r="P38">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q38">
         <v>1192.08</v>
@@ -5816,7 +5816,7 @@
         <v>54</v>
       </c>
       <c r="P39">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q39">
         <v>1710.54</v>
@@ -5935,7 +5935,7 @@
         <v>81</v>
       </c>
       <c r="P40">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q40">
         <v>953.97</v>
@@ -6054,7 +6054,7 @@
         <v>99</v>
       </c>
       <c r="P41">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q41">
         <v>948.4299999999999</v>
@@ -6292,7 +6292,7 @@
         <v>25</v>
       </c>
       <c r="P43">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q43">
         <v>961.03</v>
@@ -6411,7 +6411,7 @@
         <v>68</v>
       </c>
       <c r="P44">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q44">
         <v>175.65</v>
@@ -6530,7 +6530,7 @@
         <v>40</v>
       </c>
       <c r="P45">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q45">
         <v>2105.34</v>
@@ -6768,7 +6768,7 @@
         <v>93</v>
       </c>
       <c r="P47">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q47">
         <v>4455.3</v>
@@ -6887,7 +6887,7 @@
         <v>3</v>
       </c>
       <c r="P48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q48">
         <v>282.07</v>
@@ -7006,7 +7006,7 @@
         <v>17</v>
       </c>
       <c r="P49">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q49">
         <v>2834.16</v>
@@ -7125,7 +7125,7 @@
         <v>42</v>
       </c>
       <c r="P50">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q50">
         <v>10671.8</v>
@@ -7244,7 +7244,7 @@
         <v>15</v>
       </c>
       <c r="P51">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q51">
         <v>160.91</v>
